--- a/www/download/COUNTRY.CHN.WIOD13.xlsx
+++ b/www/download/COUNTRY.CHN.WIOD13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>China</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>8.35073066812331</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>8.31393434562861</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>8.2898114750299</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>8.27883125388176</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>8.27814537635583</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>8.27883126459024</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>8.27677527170928</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>8.27677525073227</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>8.27677538995426</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.359</t>
+          <t>8.27677526547708</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>8.19336325318561</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>7.97257413747067</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>7.60514071715928</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.646</t>
+          <t>6.9458916054178</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.646</t>
+          <t>6.83139424738295</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>680.65</t>
+          <t>-0.505213126133137</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>689.5</t>
+          <t>-0.479282896872297</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>698.2</t>
+          <t>-0.500412363181639</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>706.37</t>
+          <t>-0.511501803548544</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>713.94</t>
+          <t>-0.526274555126516</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>720.85</t>
+          <t>-0.505269869776754</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>730.25</t>
+          <t>-0.464631047110428</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>737.4</t>
+          <t>-0.443583152809506</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>744.32</t>
+          <t>-0.42040847456927</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>-0.368018271520238</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>758.25</t>
+          <t>-0.332218799374668</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>-0.32692258183145</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>769.9</t>
+          <t>-0.263480755958882</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>774.8</t>
+          <t>-0.26748249090098</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>779.95</t>
+          <t>-0.24498100941157</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>230.89</t>
+          <t>-0.394311733438367</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>239.098</t>
+          <t>-0.355066671832782</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>247.449</t>
+          <t>-0.353128095004113</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>255.805</t>
+          <t>-0.342242345341239</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>264.115</t>
+          <t>-0.342746156174521</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>272.359</t>
+          <t>-0.29773538297535</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>281.876</t>
+          <t>-0.223042270281474</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>290.801</t>
+          <t>-0.175193286788704</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>299.812</t>
+          <t>-0.104604973547073</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>309.298</t>
+          <t>-0.0106953736001085</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>318.359</t>
+          <t>0.056201979948723</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>327.313</t>
+          <t>0.0932611132631467</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>336.439</t>
+          <t>0.25230137348249</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>345.235</t>
+          <t>0.291737770811354</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>354.245</t>
+          <t>0.341715572532232</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1214994.346</t>
+          <t>-0.250925227184531</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1229546.798</t>
+          <t>-0.217945773106995</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1238180.551</t>
+          <t>-0.17192242345769</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1236037.648</t>
+          <t>-0.110187755856657</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1235342.034</t>
+          <t>-0.0454912241983799</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1260851.623</t>
+          <t>0.0812847305540521</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1339026.837</t>
+          <t>0.194973676615165</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1400107.894</t>
+          <t>0.304440879382781</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1440056.64</t>
+          <t>0.39757923576459</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1470748.352</t>
+          <t>0.421532925963999</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1476522.787</t>
+          <t>0.512313611174063</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1465602.046</t>
+          <t>0.594416630553371</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1492885.254</t>
+          <t>0.73759897720717</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1538102.906</t>
+          <t>0.765021863335619</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1555748.515</t>
+          <t>0.82312286592313</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>412150.393</t>
+          <t>1942932903015.99</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>426369.92</t>
+          <t>1995286677552.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>438823.592</t>
+          <t>2007131197410.79</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>447618.682</t>
+          <t>1985700379654.64</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>457002.426</t>
+          <t>2008988451653.39</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>476387.581</t>
+          <t>1931267571941.96</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>516864.339</t>
+          <t>1961232046012.09</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>552146.561</t>
+          <t>1994264772498.49</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>580054.797</t>
+          <t>2109465600844.85</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>604918.813</t>
+          <t>2160328522388.95</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>619932.858</t>
+          <t>2271768772140.9</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>627893.215</t>
+          <t>2492531909782.16</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>652375.947</t>
+          <t>2598081385272.28</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>685347.872</t>
+          <t>2699798810404.05</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>706605.398</t>
+          <t>2735820605069.26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>596935865098.496</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>589373076932.361</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>588142877959.792</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>573913721572.996</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>565905599900.213</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>538280143971.146</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>534254771738.9</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>534569551906.061</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>524807492602.16</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>517399537564.88</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>502172451635.601</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>13.47</t>
+          <t>490216554738.093</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>457318223940.727</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>473782249119.289</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>473619848234.327</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>44.38</t>
+          <t>24569235.1275882</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.21</t>
+          <t>21618703.1855218</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>46.03</t>
+          <t>19589964.6387571</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>18578293.1583089</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>47.58</t>
+          <t>17585620.5272961</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>48.31</t>
+          <t>15185975.8143618</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>49.02</t>
+          <t>13975545.3251904</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>12956638.9084832</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>48.52</t>
+          <t>12209822.2597021</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>11119667.6379332</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>45.89</t>
+          <t>9920870.0756531</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>44.54</t>
+          <t>8611456.91459338</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>6967911.59831604</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>5606705.55264043</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>5331395.87745202</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>7219743.96616262</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.06</t>
+          <t>7293583.5264036</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>41.84</t>
+          <t>7274826.29700395</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40.62</t>
+          <t>7210409.12226206</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>7425945.36452055</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>38.23</t>
+          <t>7811240.56749132</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>7753068.71862439</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>35.87</t>
+          <t>8112415.35776575</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>8893356.07028301</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>9932090.38230274</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>10672609.3733664</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>36.27</t>
+          <t>11524139.9019201</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>13311951.5500386</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>36.62</t>
+          <t>15159148.3148038</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>36.62</t>
+          <t>14176118.0997505</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>15126263.1888326</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>15649342.3790846</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>15641143.9338876</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>15389253.9399697</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>15907822.7321883</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>15911266.108939</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>15734730.1684648</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>16356710.9121391</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>18636486.0613312</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>21033585.3889652</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>23688938.3489101</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>27240116.9964364</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>32121699.8980419</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>36954630.0954668</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>34930683.3020388</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>44.08</t>
+          <t>-0.309556659338431</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.68</t>
+          <t>-0.276570415131229</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>45.27</t>
+          <t>-0.253882672223445</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>-0.220059277956098</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>46.41</t>
+          <t>-0.192440531132746</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>46.97</t>
+          <t>-0.114982066780616</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>47.51</t>
+          <t>-0.0325508240325502</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>48.04</t>
+          <t>0.0328806771209706</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>47.18</t>
+          <t>0.105271561580323</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>0.16915221058041</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>0.234501924664957</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>0.280848654676076</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>43.57</t>
+          <t>0.426525146747572</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>0.446546116228874</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>0.491925223886913</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>45.58</t>
+          <t>163233.598973876</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.73</t>
+          <t>183050.644197672</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>43.89</t>
+          <t>199475.469765096</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>209414.807422265</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>250458.663931067</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>236798.973178692</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>254443.457110566</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>39.67</t>
+          <t>275592.998072507</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>309925.435775457</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>358846.470547436</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>403583.103315396</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>451626.919282066</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>503932.535039312</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>41.01</t>
+          <t>645032.502948187</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>41.01</t>
+          <t>646015.05073943</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>8.35073066812331</t>
+          <t>2585.36796308923</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.31393434562861</t>
+          <t>2464.9863991707</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8.2898114750299</t>
+          <t>2376.82390808687</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>8.27883125388176</t>
+          <t>2243.56086803012</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8.27814537635583</t>
+          <t>2142.64879256077</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8.27883126459024</t>
+          <t>1976.36433405151</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8.27677527170928</t>
+          <t>1895.35059827733</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8.27677525073227</t>
+          <t>1838.26542254556</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8.27677538995426</t>
+          <t>1750.4547531582</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>8.27677526547708</t>
+          <t>1672.82101155875</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>8.19336325318561</t>
+          <t>1577.37866814403</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>7.97257413747067</t>
+          <t>1497.70019929677</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>7.60514071715928</t>
+          <t>1359.29173665578</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>6.9458916054178</t>
+          <t>1372.3456091842</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>6.83139424738295</t>
+          <t>1336.98204856019</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>-137954560980.401</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>-117723275743.485</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>-115427322672.743</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>-104282345117.07</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>-100396680551.396</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.608</t>
+          <t>-101634137686.491</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.659</t>
+          <t>-95265699267.5379</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.707</t>
+          <t>-103124778675.379</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>-124358020827.749</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-143727616093.793</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.018</t>
+          <t>-161489568619.063</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.182</t>
+          <t>-164369569010.582</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>-161506720770.689</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.906</t>
+          <t>-141355687181.894</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2.088</t>
+          <t>-117783599440.509</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>-138611698212.324</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>-118470266273.547</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>-118364787602.518</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>-107779690394.528</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>-103891953344.026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.608</t>
+          <t>-105936687090.95</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.659</t>
+          <t>-100130852830.419</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.707</t>
+          <t>-108975056818.214</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>-130320287606.992</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-149930169475.163</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.018</t>
+          <t>-167754279976.753</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.182</t>
+          <t>-170626523199.229</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>-166842938796.933</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1.906</t>
+          <t>-146693684735.486</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2.088</t>
+          <t>-122051075218.204</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.127</t>
+          <t>657137231.922848</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.361</t>
+          <t>746990530.061879</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2.489</t>
+          <t>2937464929.77431</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2.578</t>
+          <t>3497345277.45777</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.705</t>
+          <t>3495272792.62981</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.815</t>
+          <t>4302549404.45865</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.982</t>
+          <t>4865153562.8807</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3.159</t>
+          <t>5850278142.83448</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>5962266779.24362</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>3.875</t>
+          <t>6202553381.37041</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>4.349</t>
+          <t>6264711357.69039</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>4.881</t>
+          <t>6256954188.64764</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>5.606</t>
+          <t>5336218026.24394</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>7.133</t>
+          <t>5337997553.5921</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>4267475777.69546</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.889</t>
+          <t>1785.05009327472</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.229</t>
+          <t>1783.24408745923</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.481</t>
+          <t>1773.38950289721</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2.648</t>
+          <t>1749.84448336086</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.814</t>
+          <t>1730.31632088944</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.125</t>
+          <t>1749.11787821077</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.454</t>
+          <t>1833.65537447282</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3.794</t>
+          <t>1898.70883436692</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>4.458</t>
+          <t>1934.72785849886</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>5.373</t>
+          <t>1955.78238356927</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>6.527</t>
+          <t>1947.27700174926</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>1918.32728537736</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>10.741</t>
+          <t>1939.06384410565</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>13.913</t>
+          <t>1985.16121108915</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>1994.67724213095</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.728</t>
+          <t>1785.05009327472</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.856</t>
+          <t>1783.24408745923</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.953</t>
+          <t>1773.38950289721</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.019</t>
+          <t>1749.84448336086</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.083</t>
+          <t>1730.31632088944</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.198</t>
+          <t>1749.11787821077</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1833.65537447282</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>1898.70883436692</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.641</t>
+          <t>1934.72785849886</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.932</t>
+          <t>1955.78238356927</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2.257</t>
+          <t>1947.27700174926</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2.713</t>
+          <t>1918.32728537736</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>3.495</t>
+          <t>1939.06384410565</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>4.521</t>
+          <t>1985.16121108915</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>4.984</t>
+          <t>1994.67724213095</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-50.52</t>
+          <t>167973.661998802</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-47.93</t>
+          <t>171683.475331148</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-50.04</t>
+          <t>207238.754356267</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-51.15</t>
+          <t>207431.41559536</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-51.67</t>
+          <t>218500.671867043</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-50.53</t>
+          <t>279546.635422261</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-46.47</t>
+          <t>299418.561866264</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-44.36</t>
+          <t>365404.376202279</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-42.04</t>
+          <t>485016.140506976</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-36.8</t>
+          <t>655829.097530781</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-33.22</t>
+          <t>836718.788604738</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-32.69</t>
+          <t>1061578.03273553</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-26.35</t>
+          <t>1342004.10863597</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-26.75</t>
+          <t>1581532.9107827</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-24.5</t>
+          <t>1333217.07958759</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-39.43</t>
+          <t>161121418385.946</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-35.51</t>
+          <t>141583559986.909</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-35.31</t>
+          <t>142618434782.923</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-34.22</t>
+          <t>133216214793.423</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-32.95</t>
+          <t>132680162717.548</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-29.77</t>
+          <t>142693834077.757</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-22.31</t>
+          <t>140459059177.548</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-17.52</t>
+          <t>154949617124.551</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-10.46</t>
+          <t>190024758270.362</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>225504135073.02</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>259157527460.871</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>280208402101.826</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>292352097721.909</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>278566387307.207</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>234260176542.249</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-25.09</t>
+          <t>142146.183271598</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-21.8</t>
+          <t>143958.435637294</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-17.19</t>
+          <t>152472.930800699</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-11.02</t>
+          <t>152027.786600413</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>177255.904175995</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>234740.131105421</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>254919.042081741</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>308463.600901105</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>39.76</t>
+          <t>422020.14828747</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>570738.917504941</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>51.23</t>
+          <t>670058.922035534</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>59.44</t>
+          <t>802127.739298075</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>73.75</t>
+          <t>973630.835878624</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>76.51</t>
+          <t>1165162.30419468</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>82.31</t>
+          <t>1048884.49315057</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1214994.346</t>
+          <t>19179138713.2635</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1229546.798</t>
+          <t>19751003145.3682</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1238180.551</t>
+          <t>19696861097.6363</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1236037.648</t>
+          <t>20952563201.7735</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1235342.034</t>
+          <t>26080655877.4626</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1260851.623</t>
+          <t>34408259260.9711</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1339026.837</t>
+          <t>38247978678.2596</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1400107.894</t>
+          <t>43037398004.9959</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1440056.64</t>
+          <t>56493474150.3957</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1470748.352</t>
+          <t>70413545037.0581</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1476522.787</t>
+          <t>77039378696.1155</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1465602.046</t>
+          <t>86545676846.0323</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1492885.254</t>
+          <t>94179808710.6418</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1538102.906</t>
+          <t>100527342603.11</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1555748.515</t>
+          <t>88930344858.9185</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>412150.393</t>
+          <t>25827.478727204</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>426369.92</t>
+          <t>27725.0396938538</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>438823.592</t>
+          <t>54765.8235555671</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>447618.682</t>
+          <t>55403.6289949468</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>457002.426</t>
+          <t>41244.7676910472</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>476387.581</t>
+          <t>44806.5043168395</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>516864.339</t>
+          <t>44499.519784523</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>552146.561</t>
+          <t>56940.7753011736</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>580054.797</t>
+          <t>62995.9922195069</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>604918.813</t>
+          <t>85090.1800258401</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>619932.858</t>
+          <t>166659.866569204</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>627893.215</t>
+          <t>259450.293437452</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>652375.947</t>
+          <t>368373.272757344</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>685347.872</t>
+          <t>416370.606588022</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>706605.398</t>
+          <t>284332.586437023</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1943002.995</t>
+          <t>141942279672.683</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1995348.722</t>
+          <t>121832556841.541</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2007207.142</t>
+          <t>122921573685.287</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1985688.774</t>
+          <t>112263651591.65</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1960371.405</t>
+          <t>106599506840.085</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1931302.959</t>
+          <t>108285574816.786</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1961402.07</t>
+          <t>102211080499.288</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1994455.008</t>
+          <t>111912219119.556</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2109504.577</t>
+          <t>133531284119.966</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2160355.8</t>
+          <t>155090590035.962</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2271850.823</t>
+          <t>182118148764.756</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2492583.469</t>
+          <t>193662725255.794</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2598260.28</t>
+          <t>198172289011.267</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2699937.587</t>
+          <t>178039044704.097</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2735917.867</t>
+          <t>145329831683.331</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>15.125</t>
+          <t>540949.76341</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>15.649</t>
+          <t>637272.51759</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>15.641</t>
+          <t>698358.5122</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>15.389</t>
+          <t>733353.7522</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>15.823</t>
+          <t>769416.261</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>15.911</t>
+          <t>845162.8223</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>15.734</t>
+          <t>922030.66405</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>16.356</t>
+          <t>1001786.88916</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>18.636</t>
+          <t>1126891.61132</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>21.033</t>
+          <t>1338969.68842</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>23.689</t>
+          <t>1558738.41524</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>27.241</t>
+          <t>1858173.94652</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>32.121</t>
+          <t>2348695.72296</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>36.955</t>
+          <t>3032939.70854</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>34.932</t>
+          <t>3263395.75391</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>927359.119</t>
+          <t>0.0784907495285394</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>929929.814</t>
+          <t>0.0869536537099282</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>933533.435</t>
+          <t>0.0953793601736895</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>930370.776</t>
+          <t>0.103773763587297</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>937817.747</t>
+          <t>0.0994379563281661</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>948107.806</t>
+          <t>0.125639443234304</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>966369.722</t>
+          <t>0.137980383625626</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>989092.749</t>
+          <t>0.149075368800657</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1006639.806</t>
+          <t>0.161042082220849</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1020110.349</t>
+          <t>0.173620431616822</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1023503.052</t>
+          <t>0.192029526858079</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1054484.694</t>
+          <t>0.221150656896944</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1076703.09</t>
+          <t>0.271566430010195</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1107483.703</t>
+          <t>0.276268459431765</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1110293.654</t>
+          <t>0.318782068262343</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>7.219</t>
+          <t>397856.131927165</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>7.293</t>
+          <t>467727.886435222</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>7.274</t>
+          <t>515800.335953662</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>542539.536153294</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>7.569</t>
+          <t>563860.76736749</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>7.811</t>
+          <t>607903.674040208</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>7.752</t>
+          <t>659006.88251917</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>8.111</t>
+          <t>707407.939686337</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>8.893</t>
+          <t>777143.095397519</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>9.932</t>
+          <t>900055.312694353</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>10.672</t>
+          <t>1018459.84835292</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>11.524</t>
+          <t>1182195.15416825</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>13.311</t>
+          <t>1468707.44826045</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>15.159</t>
+          <t>1905657.48987876</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>14.176</t>
+          <t>2087894.22134836</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>596946.554</t>
+          <t>397856.131927165</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>589384.384</t>
+          <t>467727.886435222</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>588155.812</t>
+          <t>515800.335953662</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>573910.41</t>
+          <t>542539.536153294</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>554733.979</t>
+          <t>563860.76736749</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>538289.059</t>
+          <t>607903.674040208</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>534277.285</t>
+          <t>659006.88251917</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>534591.93</t>
+          <t>707407.939686337</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>524814.726</t>
+          <t>777143.095397519</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>517399.98</t>
+          <t>900055.312694353</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>502177.166</t>
+          <t>1018459.84835292</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>490227.056</t>
+          <t>1182195.15416825</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>457334.038</t>
+          <t>1468707.44826045</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>473774.183</t>
+          <t>1905657.48987876</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>473622.407</t>
+          <t>2087894.22134836</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-30.96</t>
+          <t>2126558.60724414</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-27.66</t>
+          <t>2361413.11970726</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-25.39</t>
+          <t>2488756.12919788</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-22.01</t>
+          <t>2578115.65116243</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-17.62</t>
+          <t>2704997.60990416</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-11.5</t>
+          <t>2815277.64064881</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>2981608.22690928</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3158527.52731261</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>3439734.60767454</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>3874822.31367192</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>4348902.36244183</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>4880878.19600143</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>5606362.67948541</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>44.66</t>
+          <t>7132996.54979171</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>49.19</t>
+          <t>7059783.82168639</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>397856.131927165</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>21.62</t>
+          <t>433774.526802564</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19.591</t>
+          <t>469333.554400443</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>18.578</t>
+          <t>494934.40106441</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>520157.755393198</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>15.186</t>
+          <t>550482.810170273</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>13.977</t>
+          <t>581579.738494437</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>12.958</t>
+          <t>618128.386225982</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>662288.426450693</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>710753.382067819</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>9.921</t>
+          <t>770227.835348201</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>8.612</t>
+          <t>842411.169520139</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>6.968</t>
+          <t>922864.559008487</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>5.607</t>
+          <t>1013220.98897476</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>5.332</t>
+          <t>1098671.54916663</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>397856.131927165</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>433774.526802564</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>469333.554400443</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>494934.40106441</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>520157.755393198</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>550482.810170273</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>581579.738494437</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>618128.386225982</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>662288.426450693</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>710753.382067819</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>770227.835348201</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>842411.169520139</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>922864.559008487</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>1013220.98897476</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1098671.54916663</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>330148.777972835</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>388384.142874778</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>436851.436996338</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>476955.571506706</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>519438.09813251</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>590508.888499792</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>665846.90408083</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>746451.654073663</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>863867.459282481</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1031594.79308565</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>1238700.76632708</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1531036.33856175</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2026432.43324955</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2615654.47089124</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2896547.53890164</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>412150392859.309</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>426369920378.008</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>438823592454.172</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>447618682394.545</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>457002425684.421</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>476387580510.376</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>516864338675.477</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>552146560740.986</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>580054796877.443</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>604918813097.261</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>619932858057.87</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>627893214636.227</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>652375946517.384</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>685347872401.688</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>706605398114.285</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1214994345987.44</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1229546798303.14</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1238180550922.83</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1236037647711.61</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1235342034135.8</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1260851622508.23</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1339026837208.78</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1400107894462.17</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1440056639637.87</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1470748352444.09</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1476522786576.37</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1465602046028.31</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1492885253576.94</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1538102906351.87</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1555748515000.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>927359118910.789</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>929929813619.566</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>933533434522.381</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>930370776087.752</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>937817747349.174</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>948107806214.009</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>966369722461.129</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>989092749439.088</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1006639805625.82</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1020110349379.16</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1023503051701.24</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1054484694103.47</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1076703089611.7</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1107483703160.28</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1110293653915.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>680650000</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>689500000</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>698200000</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>706370000</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>713940000</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>720850000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>730250000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>737400000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>744320000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>7.52e+08</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>758250000</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>7.64e+08</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>769900000</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>774800000</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>779950000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>230890099.057785</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>239097902.1753</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>247449075.19598</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>255804836.74459</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>264114959.887512</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>272358762.348075</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>281876488.827175</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>290801070.04668</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>299812086.919296</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>309297608.0464</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>318358845.45495</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>327312872.742</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>336438611.08569</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>345235373.61768</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>354245480.51664</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1214994345987.44</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1229546798303.14</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1238180550922.83</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1236037647711.61</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1235342034135.8</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1260851622508.23</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1339026837208.78</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1400107894462.17</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1440056639637.87</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1470748352444.09</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1476522786576.37</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1465602046028.31</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1492885253576.94</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1538102906351.87</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1555748515000.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>412150392859.309</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>426369920378.008</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>438823592454.172</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>447618682394.545</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>457002425684.421</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>476387580510.376</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>516864338675.477</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>552146560740.986</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>580054796877.443</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>604918813097.261</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>619932858057.87</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>627893214636.227</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>652375946517.384</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>685347872401.688</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>706605398114.285</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.0562093506386633</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.060132898282147</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.0642229342975888</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.0684802104861104</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.0729051611681329</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.0774979069224905</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.082258260780203</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.0871857366777081</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.0972163267750453</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.102690348456082</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.11899884376754</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.134733325009745</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.131794604116846</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.140604669437637</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.140604669437637</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.443790668260678</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.452136418603582</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.460255196955978</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.4681321380586</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.475753011927834</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.483104273846828</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.490173109323406</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.496947473486285</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.485234087664569</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.472155254567998</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.458939788004176</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.44538179323064</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.440040375197511</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.436009295706546</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.436009295706546</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.442857123957802</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.430587825971414</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.418379011603576</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.406244794312433</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.394198969761176</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.382254962087824</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.370425772753534</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.35872393269315</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.360406728417528</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.368011539833063</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.364918511085427</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.362742024616758</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.371022163542786</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.36624317771296</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.36624317771296</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.0463005508328902</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.0487470639722212</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.0512995826534342</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.0539610480363788</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.056734370862934</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.0596224229662163</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.0626280285504751</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.0657539552756941</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.072556037345357</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.0755835939356043</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.0867325066632651</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.097428836119497</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.0941310138522617</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.100846173037866</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.100846173037866</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.440763305854076</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.446761572997244</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.452663377317704</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.458460645622173</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.46414528481011</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.469709201971289</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.475144325035073</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.48044262388356</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.471814324658347</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.461216139244906</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.450635553120864</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.439953048243381</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.435683855712475</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.43195168744715</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.43195168744715</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.455793286170177</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.447348505887678</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.438894182886005</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.430435449198591</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.421977487184099</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.413525517919637</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.405084789271595</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.396660563697889</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.398486780853439</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.406057409676632</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.405489083073014</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.405475258494265</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.413042273292406</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.410059282372126</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.410059282372126</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1888818.00833</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2229366.1548</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2480754.93414</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2647916.15531</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2814386.86818</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>3125236.69535</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3454251.82819</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>3794147.41702</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>4457621.02152</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>5372763.54888</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>6527489.8572</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>8160175.32311</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>10740914.89603</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>13913136.42324</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>15149964.83865</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>728004.9099</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>856112.02931</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>952651.77295</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1019495.10766</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1083298.8655</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1198412.56254</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1324853.7866</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1453859.59376</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1641010.55468</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1931650.10578</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2257160.61468</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2713231.49273</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>3495139.88151</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>4521311.96077</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>4984441.76025</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>17758318.2135344</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>18774740.1683004</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>19731546.2433513</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>20612115.284853</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>21459490.3763524</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>22266287.2344285</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>23075895.8138145</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>23892605.1463974</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>24778920.3679366</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>25811464.7807498</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>26951756.7975726</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>28152579.7698671</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>29424285.0939325</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>30941003.0245525</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>32157310.8492424</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
